--- a/etf_holdings/2026-09-15_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:18</t>
+          <t>2026-09-15 19:53:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.78%3310</t>
+          <t>-5.89%3115</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-5.89%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3310</v>
+        <v>3115</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:18</t>
+          <t>2026-09-15 19:53:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.24%2380</t>
+          <t>+0.21%2385</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2380</v>
+        <v>2385</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:18</t>
+          <t>2026-09-15 19:53:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.37%5345</t>
+          <t>-4.3%5115</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5345</v>
+        <v>5115</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:18</t>
+          <t>2026-09-15 19:53:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.75%11990</t>
+          <t>-2.29%11715</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>11990</v>
+        <v>11715</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:18</t>
+          <t>2026-09-15 19:53:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.72%970</t>
+          <t>-1.96%951</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>970</v>
+        <v>951</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:18</t>
+          <t>2026-09-15 19:53:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+4.27%1955</t>
+          <t>+1.28%1980</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+4.27%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1955</v>
+        <v>1980</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:18</t>
+          <t>2026-09-15 19:53:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.53%1875</t>
+          <t>-1.87%1840</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1875</v>
+        <v>1840</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:18</t>
+          <t>2026-09-15 19:53:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-7.14%1235</t>
+          <t>-1.21%1220</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-7.14%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1235</v>
+        <v>1220</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:18</t>
+          <t>2026-09-15 19:53:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-9.98%5995</t>
+          <t>+1%6055</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-9.98%</t>
+          <t>+1%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5995</v>
+        <v>6055</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:18</t>
+          <t>2026-09-15 19:53:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0%5620</t>
+          <t>-2.77%5440</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5620</v>
+        <v>5440</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:18</t>
+          <t>2026-09-15 19:53:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.19%127.5</t>
+          <t>-4.58%114.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+1.19%</t>
+          <t>-4.58%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>127.5</v>
+        <v>114.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:18</t>
+          <t>2026-09-15 19:53:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.43%181</t>
+          <t>+0.83%182.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>181</v>
+        <v>182.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:18</t>
+          <t>2026-09-15 19:53:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.21%234</t>
+          <t>-5.34%221.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-5.34%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>234</v>
+        <v>221.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:18</t>
+          <t>2026-09-15 19:53:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+2.35%567</t>
+          <t>-1.29%537</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+2.35%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>567</v>
+        <v>537</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:18</t>
+          <t>2026-09-15 19:53:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+5.73%442.5</t>
+          <t>-2.49%431.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+5.73%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>442.5</v>
+        <v>431.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:19</t>
+          <t>2026-09-15 19:53:46</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+3.88%535</t>
+          <t>-2.8%520</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+3.88%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>535</v>
+        <v>520</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:19</t>
+          <t>2026-09-15 19:53:46</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+4.58%6400</t>
+          <t>-5.7%6035</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6400</v>
+        <v>6035</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:19</t>
+          <t>2026-09-15 19:53:46</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-2.31%1055</t>
+          <t>+2.84%1085</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1055</v>
+        <v>1085</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:19</t>
+          <t>2026-09-15 19:53:46</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.73%2270</t>
+          <t>+1.98%2315</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2270</v>
+        <v>2315</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:19</t>
+          <t>2026-09-15 19:53:46</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-1.64%3590</t>
+          <t>-6.55%3355</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>-6.55%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3590</v>
+        <v>3355</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:19</t>
+          <t>2026-09-15 19:53:46</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.92%798</t>
+          <t>-0.38%795</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.92%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:19</t>
+          <t>2026-09-15 19:53:46</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.55%4560</t>
+          <t>-2.85%4430</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4560</v>
+        <v>4430</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:19</t>
+          <t>2026-09-15 19:53:46</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.11%489.5</t>
+          <t>-2.45%477.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>489.5</v>
+        <v>477.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:19</t>
+          <t>2026-09-15 19:53:46</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-4.21%6600</t>
+          <t>-4.39%6310</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-4.21%</t>
+          <t>-4.39%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6600</v>
+        <v>6310</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:19</t>
+          <t>2026-09-15 19:53:46</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-4.36%17885</t>
+          <t>-2.56%17520</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>-2.56%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>17885</v>
+        <v>17520</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:19</t>
+          <t>2026-09-15 19:53:46</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1.18%515</t>
+          <t>+0.78%519</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+1.18%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:19</t>
+          <t>2026-09-15 19:53:46</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+0.95%5820</t>
+          <t>-8.76%5310</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>-8.76%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5820</v>
+        <v>5310</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:19</t>
+          <t>2026-09-15 19:53:46</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.75%731</t>
+          <t>-0.68%726</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:19</t>
+          <t>2026-09-15 19:53:46</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+1.08%934</t>
+          <t>-0.64%928</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:19</t>
+          <t>2026-09-15 19:53:46</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.18%277.5</t>
+          <t>-1.26%274</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>277.5</v>
+        <v>274</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:20</t>
+          <t>2026-09-15 19:53:47</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.85%703</t>
+          <t>+1.42%713</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>+1.42%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:20</t>
+          <t>2026-09-15 19:53:47</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.43%344</t>
+          <t>-0.29%343</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:20</t>
+          <t>2026-09-15 19:53:47</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.71%2810</t>
+          <t>-2.55%2675</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2810</v>
+        <v>2675</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:20</t>
+          <t>2026-09-15 19:53:47</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.12%86.6</t>
+          <t>-2.54%84.4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>86.59999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:20</t>
+          <t>2026-09-15 19:53:47</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-2.34%1250</t>
+          <t>-0.82%1215</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1250</v>
+        <v>1215</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:20</t>
+          <t>2026-09-15 19:53:47</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-0.93%2140</t>
+          <t>-2.8%2080</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2140</v>
+        <v>2080</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:20</t>
+          <t>2026-09-15 19:53:47</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.15%1365</t>
+          <t>-2.84%1370</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:20</t>
+          <t>2026-09-15 19:53:47</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1%1015</t>
+          <t>+1.97%1035</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>+1.97%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1015</v>
+        <v>1035</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:20</t>
+          <t>2026-09-15 19:53:47</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.97%612</t>
+          <t>-3.27%592</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:20</t>
+          <t>2026-09-15 19:53:47</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.39%1295</t>
+          <t>-1.16%1275</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1295</v>
+        <v>1275</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:20</t>
+          <t>2026-09-15 19:53:47</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.48%157.5</t>
+          <t>-4.08%153</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-2.48%</t>
+          <t>-4.08%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>157.5</v>
+        <v>153</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-15_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:45</t>
+          <t>2026-09-15 21:12:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:45</t>
+          <t>2026-09-15 21:12:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:45</t>
+          <t>2026-09-15 21:12:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:45</t>
+          <t>2026-09-15 21:12:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:45</t>
+          <t>2026-09-15 21:12:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:45</t>
+          <t>2026-09-15 21:12:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:45</t>
+          <t>2026-09-15 21:12:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:45</t>
+          <t>2026-09-15 21:12:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:45</t>
+          <t>2026-09-15 21:12:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:45</t>
+          <t>2026-09-15 21:12:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:45</t>
+          <t>2026-09-15 21:12:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:45</t>
+          <t>2026-09-15 21:12:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:45</t>
+          <t>2026-09-15 21:12:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:45</t>
+          <t>2026-09-15 21:12:41</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:45</t>
+          <t>2026-09-15 21:12:41</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:46</t>
+          <t>2026-09-15 21:12:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:46</t>
+          <t>2026-09-15 21:12:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:46</t>
+          <t>2026-09-15 21:12:43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:46</t>
+          <t>2026-09-15 21:12:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:46</t>
+          <t>2026-09-15 21:12:43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:46</t>
+          <t>2026-09-15 21:12:43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:46</t>
+          <t>2026-09-15 21:12:43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:46</t>
+          <t>2026-09-15 21:12:43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:46</t>
+          <t>2026-09-15 21:12:43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:46</t>
+          <t>2026-09-15 21:12:43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:46</t>
+          <t>2026-09-15 21:12:43</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:46</t>
+          <t>2026-09-15 21:12:43</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:46</t>
+          <t>2026-09-15 21:12:43</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:46</t>
+          <t>2026-09-15 21:12:43</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:46</t>
+          <t>2026-09-15 21:12:43</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:47</t>
+          <t>2026-09-15 21:12:44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:47</t>
+          <t>2026-09-15 21:12:44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:47</t>
+          <t>2026-09-15 21:12:44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:47</t>
+          <t>2026-09-15 21:12:44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:47</t>
+          <t>2026-09-15 21:12:44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:47</t>
+          <t>2026-09-15 21:12:44</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:47</t>
+          <t>2026-09-15 21:12:44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:47</t>
+          <t>2026-09-15 21:12:44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:47</t>
+          <t>2026-09-15 21:12:44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:47</t>
+          <t>2026-09-15 21:12:44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:47</t>
+          <t>2026-09-15 21:12:44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-09-15_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:41</t>
+          <t>2026-09-15 22:22:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:41</t>
+          <t>2026-09-15 22:22:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:41</t>
+          <t>2026-09-15 22:22:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:41</t>
+          <t>2026-09-15 22:22:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:41</t>
+          <t>2026-09-15 22:22:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:41</t>
+          <t>2026-09-15 22:22:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:41</t>
+          <t>2026-09-15 22:22:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:41</t>
+          <t>2026-09-15 22:22:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:41</t>
+          <t>2026-09-15 22:22:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:41</t>
+          <t>2026-09-15 22:22:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:41</t>
+          <t>2026-09-15 22:22:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:41</t>
+          <t>2026-09-15 22:22:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:41</t>
+          <t>2026-09-15 22:22:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:41</t>
+          <t>2026-09-15 22:22:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:41</t>
+          <t>2026-09-15 22:22:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:43</t>
+          <t>2026-09-15 22:22:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:43</t>
+          <t>2026-09-15 22:22:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:43</t>
+          <t>2026-09-15 22:22:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:43</t>
+          <t>2026-09-15 22:22:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:43</t>
+          <t>2026-09-15 22:22:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:43</t>
+          <t>2026-09-15 22:22:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:43</t>
+          <t>2026-09-15 22:22:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:43</t>
+          <t>2026-09-15 22:22:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:43</t>
+          <t>2026-09-15 22:22:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:43</t>
+          <t>2026-09-15 22:22:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:43</t>
+          <t>2026-09-15 22:22:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:43</t>
+          <t>2026-09-15 22:22:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:43</t>
+          <t>2026-09-15 22:22:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:43</t>
+          <t>2026-09-15 22:22:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:43</t>
+          <t>2026-09-15 22:22:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:44</t>
+          <t>2026-09-15 22:23:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:44</t>
+          <t>2026-09-15 22:23:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:44</t>
+          <t>2026-09-15 22:23:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:44</t>
+          <t>2026-09-15 22:23:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:44</t>
+          <t>2026-09-15 22:23:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:44</t>
+          <t>2026-09-15 22:23:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:44</t>
+          <t>2026-09-15 22:23:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:44</t>
+          <t>2026-09-15 22:23:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:44</t>
+          <t>2026-09-15 22:23:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:44</t>
+          <t>2026-09-15 22:23:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:44</t>
+          <t>2026-09-15 22:23:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-09-15_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:58</t>
+          <t>2026-09-15 22:28:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:58</t>
+          <t>2026-09-15 22:28:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:58</t>
+          <t>2026-09-15 22:28:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:58</t>
+          <t>2026-09-15 22:28:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:58</t>
+          <t>2026-09-15 22:28:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:58</t>
+          <t>2026-09-15 22:28:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:58</t>
+          <t>2026-09-15 22:28:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:58</t>
+          <t>2026-09-15 22:28:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:58</t>
+          <t>2026-09-15 22:28:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:58</t>
+          <t>2026-09-15 22:28:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:58</t>
+          <t>2026-09-15 22:28:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:58</t>
+          <t>2026-09-15 22:28:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:58</t>
+          <t>2026-09-15 22:28:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:58</t>
+          <t>2026-09-15 22:28:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:58</t>
+          <t>2026-09-15 22:28:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:59</t>
+          <t>2026-09-15 22:28:54</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:59</t>
+          <t>2026-09-15 22:28:54</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:59</t>
+          <t>2026-09-15 22:28:54</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:59</t>
+          <t>2026-09-15 22:28:54</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:59</t>
+          <t>2026-09-15 22:28:54</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:59</t>
+          <t>2026-09-15 22:28:54</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:59</t>
+          <t>2026-09-15 22:28:54</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:59</t>
+          <t>2026-09-15 22:28:54</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:59</t>
+          <t>2026-09-15 22:28:54</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:59</t>
+          <t>2026-09-15 22:28:54</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:59</t>
+          <t>2026-09-15 22:28:54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:59</t>
+          <t>2026-09-15 22:28:54</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:59</t>
+          <t>2026-09-15 22:28:54</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:59</t>
+          <t>2026-09-15 22:28:54</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:59</t>
+          <t>2026-09-15 22:28:54</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:00</t>
+          <t>2026-09-15 22:28:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:00</t>
+          <t>2026-09-15 22:28:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:00</t>
+          <t>2026-09-15 22:28:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:00</t>
+          <t>2026-09-15 22:28:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:00</t>
+          <t>2026-09-15 22:28:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:00</t>
+          <t>2026-09-15 22:28:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:00</t>
+          <t>2026-09-15 22:28:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:00</t>
+          <t>2026-09-15 22:28:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:00</t>
+          <t>2026-09-15 22:28:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:00</t>
+          <t>2026-09-15 22:28:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:00</t>
+          <t>2026-09-15 22:28:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
